--- a/entornos-de-desarrollo/apuntes/0/ed-0-contenidos-criterios-evaluacion.xlsx
+++ b/entornos-de-desarrollo/apuntes/0/ed-0-contenidos-criterios-evaluacion.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="11730" yWindow="450" windowWidth="11070" windowHeight="11670"/>
+    <workbookView xWindow="11730" yWindow="450" windowWidth="11070" windowHeight="11670" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RA Y UNIDADES" sheetId="1" r:id="rId1"/>
     <sheet name="(copia)" sheetId="2" r:id="rId2"/>
+    <sheet name="progciclo" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="77">
   <si>
     <t>RA1</t>
   </si>
@@ -886,7 +887,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -966,27 +967,51 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1017,29 +1042,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1348,7 +1370,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1375,24 +1397,24 @@
         <f>SUM(C4:C49)</f>
         <v>1</v>
       </c>
-      <c r="F1" s="28">
+      <c r="F1" s="42">
         <f>SUM(F2:H2)</f>
         <v>0.99999999999999933</v>
       </c>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:11" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="50" t="s">
         <v>25</v>
       </c>
       <c r="F2" s="19">
@@ -1407,7 +1429,7 @@
         <f>SUM(H4:H49)/SUM($F4:$H49)</f>
         <v>9.7222222222222182E-2</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="44" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1415,10 +1437,10 @@
       <c r="A3" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="43"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="51"/>
       <c r="F3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1428,7 +1450,7 @@
       <c r="H3" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I3" s="37"/>
+      <c r="I3" s="45"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
@@ -1438,7 +1460,7 @@
       <c r="B4" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="40">
         <v>0.05</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -1462,7 +1484,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="31"/>
-      <c r="C5" s="47"/>
+      <c r="C5" s="54"/>
       <c r="D5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1482,7 +1504,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" s="31"/>
-      <c r="C6" s="47"/>
+      <c r="C6" s="54"/>
       <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
@@ -1502,7 +1524,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="31"/>
-      <c r="C7" s="47"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1522,7 +1544,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="31"/>
-      <c r="C8" s="47"/>
+      <c r="C8" s="54"/>
       <c r="D8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1543,7 +1565,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" s="31"/>
-      <c r="C9" s="47"/>
+      <c r="C9" s="54"/>
       <c r="D9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1563,7 +1585,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="32"/>
-      <c r="C10" s="48"/>
+      <c r="C10" s="55"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
       </c>
@@ -1589,7 +1611,7 @@
       <c r="B11" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="46">
+      <c r="C11" s="40">
         <v>0.05</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -1615,7 +1637,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" s="31"/>
-      <c r="C12" s="47"/>
+      <c r="C12" s="54"/>
       <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
@@ -1637,7 +1659,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" s="31"/>
-      <c r="C13" s="47"/>
+      <c r="C13" s="54"/>
       <c r="D13" s="1" t="s">
         <v>6</v>
       </c>
@@ -1659,7 +1681,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" s="31"/>
-      <c r="C14" s="47"/>
+      <c r="C14" s="54"/>
       <c r="D14" s="1" t="s">
         <v>7</v>
       </c>
@@ -1681,7 +1703,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" s="31"/>
-      <c r="C15" s="47"/>
+      <c r="C15" s="54"/>
       <c r="D15" s="1" t="s">
         <v>8</v>
       </c>
@@ -1703,7 +1725,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" s="31"/>
-      <c r="C16" s="47"/>
+      <c r="C16" s="54"/>
       <c r="D16" s="1" t="s">
         <v>9</v>
       </c>
@@ -1723,7 +1745,7 @@
     </row>
     <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="32"/>
-      <c r="C17" s="48"/>
+      <c r="C17" s="55"/>
       <c r="D17" s="4" t="s">
         <v>10</v>
       </c>
@@ -1751,7 +1773,7 @@
       <c r="B18" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="46">
+      <c r="C18" s="40">
         <v>0.25</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -1770,7 +1792,7 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="H18" s="15"/>
-      <c r="I18" s="50" t="s">
+      <c r="I18" s="36" t="s">
         <v>15</v>
       </c>
       <c r="J18" s="16" t="s">
@@ -1779,7 +1801,7 @@
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="31"/>
-      <c r="C19" s="49"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="1" t="s">
         <v>18</v>
       </c>
@@ -1796,14 +1818,14 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="H19" s="13"/>
-      <c r="I19" s="51"/>
+      <c r="I19" s="37"/>
       <c r="J19" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20" s="31"/>
-      <c r="C20" s="49"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="1" t="s">
         <v>4</v>
       </c>
@@ -1820,7 +1842,7 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="H20" s="13"/>
-      <c r="I20" s="50" t="s">
+      <c r="I20" s="36" t="s">
         <v>16</v>
       </c>
       <c r="J20" s="16" t="s">
@@ -1829,7 +1851,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21" s="31"/>
-      <c r="C21" s="49"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="1" t="s">
         <v>5</v>
       </c>
@@ -1843,14 +1865,14 @@
         <f>1/9</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="I21" s="52"/>
+      <c r="I21" s="38"/>
       <c r="J21" s="16" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B22" s="31"/>
-      <c r="C22" s="49"/>
+      <c r="C22" s="41"/>
       <c r="D22" s="1" t="s">
         <v>6</v>
       </c>
@@ -1867,14 +1889,14 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="H22" s="13"/>
-      <c r="I22" s="52"/>
+      <c r="I22" s="38"/>
       <c r="J22" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B23" s="31"/>
-      <c r="C23" s="49"/>
+      <c r="C23" s="41"/>
       <c r="D23" s="1" t="s">
         <v>7</v>
       </c>
@@ -1891,14 +1913,14 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="H23" s="13"/>
-      <c r="I23" s="52"/>
+      <c r="I23" s="38"/>
       <c r="J23" s="16" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B24" s="31"/>
-      <c r="C24" s="49"/>
+      <c r="C24" s="41"/>
       <c r="D24" s="1" t="s">
         <v>8</v>
       </c>
@@ -1915,14 +1937,14 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="H24" s="13"/>
-      <c r="I24" s="52"/>
+      <c r="I24" s="38"/>
       <c r="J24" s="17" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B25" s="31"/>
-      <c r="C25" s="49"/>
+      <c r="C25" s="41"/>
       <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
@@ -1939,14 +1961,14 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="H25" s="13"/>
-      <c r="I25" s="53"/>
+      <c r="I25" s="39"/>
       <c r="J25" s="16" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="32"/>
-      <c r="C26" s="28"/>
+      <c r="C26" s="42"/>
       <c r="D26" s="4" t="s">
         <v>20</v>
       </c>
@@ -1960,7 +1982,7 @@
         <f>1/9</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="I26" s="51"/>
+      <c r="I26" s="37"/>
       <c r="J26" s="18" t="s">
         <v>62</v>
       </c>
@@ -1973,7 +1995,7 @@
       <c r="B27" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="46">
+      <c r="C27" s="40">
         <v>0.25</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -2002,7 +2024,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B28" s="31"/>
-      <c r="C28" s="49"/>
+      <c r="C28" s="41"/>
       <c r="D28" s="1" t="s">
         <v>5</v>
       </c>
@@ -2026,7 +2048,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B29" s="31"/>
-      <c r="C29" s="49"/>
+      <c r="C29" s="41"/>
       <c r="D29" s="1" t="s">
         <v>6</v>
       </c>
@@ -2050,7 +2072,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" s="31"/>
-      <c r="C30" s="49"/>
+      <c r="C30" s="41"/>
       <c r="D30" s="1" t="s">
         <v>7</v>
       </c>
@@ -2074,7 +2096,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B31" s="31"/>
-      <c r="C31" s="49"/>
+      <c r="C31" s="41"/>
       <c r="D31" s="1" t="s">
         <v>8</v>
       </c>
@@ -2098,7 +2120,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B32" s="31"/>
-      <c r="C32" s="49"/>
+      <c r="C32" s="41"/>
       <c r="D32" s="1" t="s">
         <v>9</v>
       </c>
@@ -2122,7 +2144,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B33" s="31"/>
-      <c r="C33" s="49"/>
+      <c r="C33" s="41"/>
       <c r="D33" s="1" t="s">
         <v>10</v>
       </c>
@@ -2146,7 +2168,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B34" s="31"/>
-      <c r="C34" s="49"/>
+      <c r="C34" s="41"/>
       <c r="D34" s="1" t="s">
         <v>18</v>
       </c>
@@ -2170,7 +2192,7 @@
     </row>
     <row r="35" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="32"/>
-      <c r="C35" s="28"/>
+      <c r="C35" s="42"/>
       <c r="D35" s="4" t="s">
         <v>20</v>
       </c>
@@ -2197,7 +2219,7 @@
       <c r="B36" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="46">
+      <c r="C36" s="40">
         <v>0.2</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -2225,7 +2247,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B37" s="31"/>
-      <c r="C37" s="49"/>
+      <c r="C37" s="41"/>
       <c r="D37" s="1" t="s">
         <v>5</v>
       </c>
@@ -2249,7 +2271,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B38" s="31"/>
-      <c r="C38" s="49"/>
+      <c r="C38" s="41"/>
       <c r="D38" s="1" t="s">
         <v>6</v>
       </c>
@@ -2273,7 +2295,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" s="31"/>
-      <c r="C39" s="49"/>
+      <c r="C39" s="41"/>
       <c r="D39" s="1" t="s">
         <v>7</v>
       </c>
@@ -2297,7 +2319,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B40" s="31"/>
-      <c r="C40" s="49"/>
+      <c r="C40" s="41"/>
       <c r="D40" s="1" t="s">
         <v>8</v>
       </c>
@@ -2321,7 +2343,7 @@
     </row>
     <row r="41" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="32"/>
-      <c r="C41" s="28"/>
+      <c r="C41" s="42"/>
       <c r="D41" s="4" t="s">
         <v>9</v>
       </c>
@@ -2351,7 +2373,7 @@
       <c r="B42" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="46">
+      <c r="C42" s="40">
         <v>0.2</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -2377,7 +2399,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" s="31"/>
-      <c r="C43" s="47"/>
+      <c r="C43" s="54"/>
       <c r="D43" s="1" t="s">
         <v>5</v>
       </c>
@@ -2401,7 +2423,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B44" s="31"/>
-      <c r="C44" s="47"/>
+      <c r="C44" s="54"/>
       <c r="D44" s="1" t="s">
         <v>6</v>
       </c>
@@ -2425,7 +2447,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B45" s="31"/>
-      <c r="C45" s="47"/>
+      <c r="C45" s="54"/>
       <c r="D45" s="1" t="s">
         <v>7</v>
       </c>
@@ -2449,7 +2471,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B46" s="31"/>
-      <c r="C46" s="47"/>
+      <c r="C46" s="54"/>
       <c r="D46" s="1" t="s">
         <v>8</v>
       </c>
@@ -2473,7 +2495,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B47" s="31"/>
-      <c r="C47" s="47"/>
+      <c r="C47" s="54"/>
       <c r="D47" s="1" t="s">
         <v>9</v>
       </c>
@@ -2497,7 +2519,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B48" s="31"/>
-      <c r="C48" s="47"/>
+      <c r="C48" s="54"/>
       <c r="D48" s="1" t="s">
         <v>10</v>
       </c>
@@ -2521,7 +2543,7 @@
     </row>
     <row r="49" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="32"/>
-      <c r="C49" s="48"/>
+      <c r="C49" s="55"/>
       <c r="D49" s="4" t="s">
         <v>18</v>
       </c>
@@ -2544,42 +2566,33 @@
       </c>
     </row>
     <row r="50" spans="2:23" ht="124.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="29" t="s">
+      <c r="B50" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="29"/>
-      <c r="J50" s="29"/>
-      <c r="K50" s="29"/>
-      <c r="L50" s="29"/>
-      <c r="M50" s="29"/>
-      <c r="N50" s="29"/>
-      <c r="O50" s="29"/>
-      <c r="P50" s="29"/>
-      <c r="Q50" s="29"/>
-      <c r="R50" s="29"/>
-      <c r="S50" s="29"/>
-      <c r="T50" s="29"/>
-      <c r="U50" s="29"/>
-      <c r="V50" s="29"/>
-      <c r="W50" s="29"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+      <c r="L50" s="43"/>
+      <c r="M50" s="43"/>
+      <c r="N50" s="43"/>
+      <c r="O50" s="43"/>
+      <c r="P50" s="43"/>
+      <c r="Q50" s="43"/>
+      <c r="R50" s="43"/>
+      <c r="S50" s="43"/>
+      <c r="T50" s="43"/>
+      <c r="U50" s="43"/>
+      <c r="V50" s="43"/>
+      <c r="W50" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="B42:B49"/>
-    <mergeCell ref="I36:I49"/>
-    <mergeCell ref="B18:B26"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I26"/>
-    <mergeCell ref="B27:B35"/>
-    <mergeCell ref="I27:I35"/>
-    <mergeCell ref="C27:C35"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="B50:W50"/>
     <mergeCell ref="B11:B17"/>
@@ -2596,6 +2609,15 @@
     <mergeCell ref="C18:C26"/>
     <mergeCell ref="C36:C41"/>
     <mergeCell ref="C42:C49"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="B42:B49"/>
+    <mergeCell ref="I36:I49"/>
+    <mergeCell ref="B18:B26"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I26"/>
+    <mergeCell ref="B27:B35"/>
+    <mergeCell ref="I27:I35"/>
+    <mergeCell ref="C27:C35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2608,16 +2630,16 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="50" t="s">
         <v>25</v>
       </c>
       <c r="E1" s="19">
@@ -2632,15 +2654,15 @@
         <f>SUM(G3:G48)/SUM($E3:$G48)</f>
         <v>9.7222222222222182E-2</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="44" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="51"/>
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
@@ -2650,13 +2672,13 @@
       <c r="G2" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="37"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="46">
+      <c r="B3" s="40">
         <v>0.05</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -2680,7 +2702,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="31"/>
-      <c r="B4" s="47"/>
+      <c r="B4" s="54"/>
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
@@ -2700,7 +2722,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="31"/>
-      <c r="B5" s="47"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
@@ -2720,7 +2742,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="31"/>
-      <c r="B6" s="47"/>
+      <c r="B6" s="54"/>
       <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
@@ -2740,7 +2762,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="31"/>
-      <c r="B7" s="47"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
@@ -2760,7 +2782,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="31"/>
-      <c r="B8" s="47"/>
+      <c r="B8" s="54"/>
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
@@ -2780,7 +2802,7 @@
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="32"/>
-      <c r="B9" s="48"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="21" t="s">
         <v>10</v>
       </c>
@@ -2802,7 +2824,7 @@
       <c r="A10" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="40">
         <v>0.05</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -2828,7 +2850,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="31"/>
-      <c r="B11" s="47"/>
+      <c r="B11" s="54"/>
       <c r="C11" s="1" t="s">
         <v>5</v>
       </c>
@@ -2850,7 +2872,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="31"/>
-      <c r="B12" s="47"/>
+      <c r="B12" s="54"/>
       <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
@@ -2872,7 +2894,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="31"/>
-      <c r="B13" s="47"/>
+      <c r="B13" s="54"/>
       <c r="C13" s="1" t="s">
         <v>7</v>
       </c>
@@ -2894,7 +2916,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="31"/>
-      <c r="B14" s="47"/>
+      <c r="B14" s="54"/>
       <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
@@ -2916,7 +2938,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="31"/>
-      <c r="B15" s="47"/>
+      <c r="B15" s="54"/>
       <c r="C15" s="1" t="s">
         <v>9</v>
       </c>
@@ -2936,7 +2958,7 @@
     </row>
     <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="32"/>
-      <c r="B16" s="48"/>
+      <c r="B16" s="55"/>
       <c r="C16" s="21" t="s">
         <v>10</v>
       </c>
@@ -2960,7 +2982,7 @@
       <c r="A17" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="46">
+      <c r="B17" s="40">
         <v>0.25</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -2979,7 +3001,7 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="G17" s="15"/>
-      <c r="H17" s="50" t="s">
+      <c r="H17" s="36" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="16" t="s">
@@ -2988,7 +3010,7 @@
     </row>
     <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="31"/>
-      <c r="B18" s="49"/>
+      <c r="B18" s="41"/>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
@@ -3005,14 +3027,14 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="G18" s="13"/>
-      <c r="H18" s="51"/>
+      <c r="H18" s="37"/>
       <c r="I18" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="31"/>
-      <c r="B19" s="49"/>
+      <c r="B19" s="41"/>
       <c r="C19" s="1" t="s">
         <v>4</v>
       </c>
@@ -3029,7 +3051,7 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="G19" s="13"/>
-      <c r="H19" s="50" t="s">
+      <c r="H19" s="36" t="s">
         <v>16</v>
       </c>
       <c r="I19" s="16" t="s">
@@ -3038,7 +3060,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="31"/>
-      <c r="B20" s="49"/>
+      <c r="B20" s="41"/>
       <c r="C20" s="1" t="s">
         <v>5</v>
       </c>
@@ -3052,14 +3074,14 @@
         <f>1/9</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="H20" s="52"/>
+      <c r="H20" s="38"/>
       <c r="I20" s="16" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="31"/>
-      <c r="B21" s="49"/>
+      <c r="B21" s="41"/>
       <c r="C21" s="1" t="s">
         <v>6</v>
       </c>
@@ -3076,14 +3098,14 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="G21" s="13"/>
-      <c r="H21" s="52"/>
+      <c r="H21" s="38"/>
       <c r="I21" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="31"/>
-      <c r="B22" s="49"/>
+      <c r="B22" s="41"/>
       <c r="C22" s="1" t="s">
         <v>7</v>
       </c>
@@ -3100,14 +3122,14 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="G22" s="13"/>
-      <c r="H22" s="52"/>
+      <c r="H22" s="38"/>
       <c r="I22" s="16" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="31"/>
-      <c r="B23" s="49"/>
+      <c r="B23" s="41"/>
       <c r="C23" s="1" t="s">
         <v>8</v>
       </c>
@@ -3124,14 +3146,14 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="G23" s="13"/>
-      <c r="H23" s="52"/>
+      <c r="H23" s="38"/>
       <c r="I23" s="17" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="31"/>
-      <c r="B24" s="49"/>
+      <c r="B24" s="41"/>
       <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
@@ -3148,14 +3170,14 @@
         <v>1.1111111111111112E-2</v>
       </c>
       <c r="G24" s="13"/>
-      <c r="H24" s="53"/>
+      <c r="H24" s="39"/>
       <c r="I24" s="16" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="32"/>
-      <c r="B25" s="28"/>
+      <c r="B25" s="42"/>
       <c r="C25" s="21" t="s">
         <v>20</v>
       </c>
@@ -3169,7 +3191,7 @@
         <f>1/9</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="H25" s="51"/>
+      <c r="H25" s="37"/>
       <c r="I25" s="18" t="s">
         <v>62</v>
       </c>
@@ -3178,7 +3200,7 @@
       <c r="A26" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="46">
+      <c r="B26" s="40">
         <v>0.25</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -3206,7 +3228,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="31"/>
-      <c r="B27" s="49"/>
+      <c r="B27" s="41"/>
       <c r="C27" s="1" t="s">
         <v>5</v>
       </c>
@@ -3230,7 +3252,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="31"/>
-      <c r="B28" s="49"/>
+      <c r="B28" s="41"/>
       <c r="C28" s="1" t="s">
         <v>6</v>
       </c>
@@ -3254,7 +3276,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="31"/>
-      <c r="B29" s="49"/>
+      <c r="B29" s="41"/>
       <c r="C29" s="1" t="s">
         <v>7</v>
       </c>
@@ -3278,7 +3300,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="31"/>
-      <c r="B30" s="49"/>
+      <c r="B30" s="41"/>
       <c r="C30" s="1" t="s">
         <v>8</v>
       </c>
@@ -3302,7 +3324,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="31"/>
-      <c r="B31" s="49"/>
+      <c r="B31" s="41"/>
       <c r="C31" s="1" t="s">
         <v>9</v>
       </c>
@@ -3326,7 +3348,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="31"/>
-      <c r="B32" s="49"/>
+      <c r="B32" s="41"/>
       <c r="C32" s="1" t="s">
         <v>10</v>
       </c>
@@ -3350,7 +3372,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="31"/>
-      <c r="B33" s="49"/>
+      <c r="B33" s="41"/>
       <c r="C33" s="1" t="s">
         <v>18</v>
       </c>
@@ -3374,7 +3396,7 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="32"/>
-      <c r="B34" s="28"/>
+      <c r="B34" s="42"/>
       <c r="C34" s="21" t="s">
         <v>20</v>
       </c>
@@ -3397,7 +3419,7 @@
       <c r="A35" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="46">
+      <c r="B35" s="40">
         <v>0.2</v>
       </c>
       <c r="C35" s="3" t="s">
@@ -3425,7 +3447,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="31"/>
-      <c r="B36" s="49"/>
+      <c r="B36" s="41"/>
       <c r="C36" s="1" t="s">
         <v>5</v>
       </c>
@@ -3449,7 +3471,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="31"/>
-      <c r="B37" s="49"/>
+      <c r="B37" s="41"/>
       <c r="C37" s="1" t="s">
         <v>6</v>
       </c>
@@ -3473,7 +3495,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="31"/>
-      <c r="B38" s="49"/>
+      <c r="B38" s="41"/>
       <c r="C38" s="1" t="s">
         <v>7</v>
       </c>
@@ -3497,7 +3519,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="31"/>
-      <c r="B39" s="49"/>
+      <c r="B39" s="41"/>
       <c r="C39" s="1" t="s">
         <v>8</v>
       </c>
@@ -3521,7 +3543,7 @@
     </row>
     <row r="40" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="32"/>
-      <c r="B40" s="28"/>
+      <c r="B40" s="42"/>
       <c r="C40" s="21" t="s">
         <v>9</v>
       </c>
@@ -3547,7 +3569,7 @@
       <c r="A41" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B41" s="46">
+      <c r="B41" s="40">
         <v>0.2</v>
       </c>
       <c r="C41" s="3" t="s">
@@ -3573,7 +3595,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="31"/>
-      <c r="B42" s="47"/>
+      <c r="B42" s="54"/>
       <c r="C42" s="1" t="s">
         <v>5</v>
       </c>
@@ -3597,7 +3619,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="31"/>
-      <c r="B43" s="47"/>
+      <c r="B43" s="54"/>
       <c r="C43" s="1" t="s">
         <v>6</v>
       </c>
@@ -3621,7 +3643,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="31"/>
-      <c r="B44" s="47"/>
+      <c r="B44" s="54"/>
       <c r="C44" s="1" t="s">
         <v>7</v>
       </c>
@@ -3645,7 +3667,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="31"/>
-      <c r="B45" s="47"/>
+      <c r="B45" s="54"/>
       <c r="C45" s="1" t="s">
         <v>8</v>
       </c>
@@ -3669,7 +3691,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="31"/>
-      <c r="B46" s="47"/>
+      <c r="B46" s="54"/>
       <c r="C46" s="1" t="s">
         <v>9</v>
       </c>
@@ -3693,7 +3715,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="31"/>
-      <c r="B47" s="47"/>
+      <c r="B47" s="54"/>
       <c r="C47" s="1" t="s">
         <v>10</v>
       </c>
@@ -3717,7 +3739,7 @@
     </row>
     <row r="48" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="32"/>
-      <c r="B48" s="48"/>
+      <c r="B48" s="55"/>
       <c r="C48" s="21" t="s">
         <v>18</v>
       </c>
@@ -3741,6 +3763,21 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="H3:H9"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A10:A16"/>
+    <mergeCell ref="B10:B16"/>
+    <mergeCell ref="H10:H16"/>
+    <mergeCell ref="A17:A25"/>
+    <mergeCell ref="B17:B25"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H25"/>
     <mergeCell ref="A26:A34"/>
     <mergeCell ref="B26:B34"/>
     <mergeCell ref="H26:H34"/>
@@ -3749,21 +3786,476 @@
     <mergeCell ref="H35:H48"/>
     <mergeCell ref="A41:A48"/>
     <mergeCell ref="B41:B48"/>
-    <mergeCell ref="A10:A16"/>
-    <mergeCell ref="B10:B16"/>
-    <mergeCell ref="H10:H16"/>
-    <mergeCell ref="A17:A25"/>
-    <mergeCell ref="B17:B25"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H25"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="H3:H9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5" style="1"/>
+    <col min="2" max="2" width="4" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="44.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="16384" width="11.5" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="6">
+        <f>SUM(C4:C22)</f>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="F1" s="28"/>
+    </row>
+    <row r="2" spans="1:7" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="19">
+        <f>SUM(F4:F22)/SUM($F4:$F22)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="47"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="57">
+        <v>0.05</v>
+      </c>
+      <c r="D4" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="26">
+        <f>SUM(F4:F4)</f>
+        <v>0.15</v>
+      </c>
+      <c r="F4" s="14">
+        <v>0.15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="57">
+        <v>0.05</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="26">
+        <f>SUM(F5:F5)</f>
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="57">
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="26">
+        <f>SUM(F6:F6)</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F6" s="13">
+        <f>1/9</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="57">
+        <v>0.25</v>
+      </c>
+      <c r="D7" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="26">
+        <f>SUM(F7:F7)</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F7" s="13">
+        <f>1/9</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="56" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="57">
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="27">
+        <f>SUM(F8:F8)</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F8" s="13">
+        <f>1/9</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <f>SUM(E9:E14)</f>
+        <v>0</v>
+      </c>
+      <c r="B9" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="26">
+        <f>SUM(F9:F9)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="26">
+        <f>SUM(F10:F10)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="26">
+        <f>SUM(F11:F11)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="26">
+        <f>SUM(F12:F12)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="26">
+        <f>SUM(F13:F13)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="27">
+        <f>SUM(F14:F14)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
+        <f>SUM(E15:E22)</f>
+        <v>0</v>
+      </c>
+      <c r="B15" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="26">
+        <f>SUM(F15:F15)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="26">
+        <f>SUM(F16:F16)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="11"/>
+      <c r="G16" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="26">
+        <f>SUM(F17:F17)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="11"/>
+      <c r="G17" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="26">
+        <f>SUM(F18:F18)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="11"/>
+      <c r="G18" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="26">
+        <f>SUM(F19:F19)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="11"/>
+      <c r="G19" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="26">
+        <f>SUM(F20:F20)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="11"/>
+      <c r="G20" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="26">
+        <f>SUM(F21:F21)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="11"/>
+      <c r="G21" s="18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="57">
+        <v>0.2</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="27">
+        <f>SUM(F22:F22)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" ht="124.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="43"/>
+      <c r="R23" s="43"/>
+      <c r="S23" s="43"/>
+      <c r="T23" s="43"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B23:T23"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
